--- a/crawl-job/results.xlsx
+++ b/crawl-job/results.xlsx
@@ -1,34 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="FB_Posts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FB_Posts" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="2">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +65,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -199,6 +152,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,6 +187,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,20 +222,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -402,91 +353,1444 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H45"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" customWidth="1"/>
+    <col min="3" max="3" width="75.83203125" customWidth="1"/>
+    <col min="4" max="4" width="65.83203125" customWidth="1"/>
+    <col min="5" max="5" width="75.83203125" customWidth="1"/>
+    <col min="6" max="6" width="68.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Link Bài Viết</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Từ Khóa Khớp</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Nội Dung Bài (Trích Đoạn)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Link Group</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Thời Gian Cào</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="str">
+        <v>STT</v>
+      </c>
+      <c r="B1" s="1" t="str">
+        <v>Tác Giả</v>
+      </c>
+      <c r="C1" s="1" t="str">
+        <v>Link Bài Viết</v>
+      </c>
+      <c r="D1" s="1" t="str">
+        <v>Từ Khóa Khớp</v>
+      </c>
+      <c r="E1" s="1" t="str">
+        <v>Nội Dung Bài (Trích Đoạn)</v>
+      </c>
+      <c r="F1" s="1" t="str">
+        <v>Link Group</v>
+      </c>
+      <c r="G1" s="1" t="str">
+        <v>Thời Gian Đăng</v>
+      </c>
+      <c r="H1" s="1" t="str">
+        <v>Thời Gian Cào</v>
+      </c>
+    </row>
+    <row r="2" ht="108" customHeight="1" xml:space="preserve">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/123/posts/9999</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>khuyến mãi, giảm giá</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Chương trình khuyến mãi giảm giá cực sốc hôm nay!</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/groups/123</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-09-10 16:19:34</t>
-        </is>
+      <c r="B2" s="1" t="str">
+        <v>Nguyễn Mỹ Hiền</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang/posts/2735444200209934/</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E2" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[AVEPOINT CHIÊU MỘ FRESHER - JUNIOR TẠI ĐÀ NẴNG - HÀ NỘI]
+ Mùa trăng này, mình đang còn thiếu khá nhiều cầu Fresher - Junior để phá cỗ, rước đèn và ăn bánh trung thu cùng.
+Một số jobs đã về đích rồi, nhưng vẫn có nhiều jobs open đang open các bạn sinh viên mới ra trường để thử sức và training nha 
+ ...</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang?locale=vi_VN</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v>3 ngày</v>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v>2026-09-14 13:31:48</v>
+      </c>
+    </row>
+    <row r="3" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v>Ngô Thuỳ Trang</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang/posts/2735428136878207/</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <v>Thực tập sinh, thực tập, intern</v>
+      </c>
+      <c r="E3" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">VR360 TUYỂN DỤNG: KINH DOANH &amp; BIÊN TẬP VIÊN NỘI DUNG VR (Có nhận Intern) 
+ Bạn đam mê công nghệ 3D/VR/AR? Bạn muốn thử sức trong môi trường thực tế ảo cực chất? VR360 đang tìm kiếm đồng đội nhiệt huyết gia nhập team cho 2 vị trí "hot":
+ CÁC VỊ TRÍ TUYỂN DỤNG:
+ Chuyên viên / Thực tập sinh Kinh doan...</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang?locale=vi_VN</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <v>2 ngày</v>
+      </c>
+      <c r="H3" s="1" t="str">
+        <v>2026-09-14 13:31:51</v>
+      </c>
+    </row>
+    <row r="4" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <v>Công Ty Tnhh Mtv Rgm Đà Nẵng</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang/posts/2738352053252482/</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <v>chưa có kinh nghiệm</v>
+      </c>
+      <c r="E4" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">RGM TD: Nhân viên IT (Biết tiếng Trung)
+------------------------
+Làm việc tại: Công ty TNHH MTV RGM Đà Nẵng
+MÔ TẢ CÔNG VIỆC:
+Hỗ trợ các phần mềm cho nhà mày
+Chưa có kinh nghiệm sẽ được đào tạo
+QUYỀN LỢI:
+- Chuyên cần tháng: 500.000
+- Chuyên cần Qúy: 1.500.000
+- Xăng xe: 200.000
+- Con nhỏ, Thâm niên:...</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang?locale=vi_VN</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H4" s="1" t="str">
+        <v>2026-09-14 13:32:07</v>
+      </c>
+    </row>
+    <row r="5" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <v>Khanh Ly</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang/posts/2722773478143673/</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E5" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Viettel Peru (Bitel) Chiêu mộ FRESHER Kỹ sư Thiết kế &amp; Triển khai Mạng Truyền dẫn
+Team mình tìm kiếm 01 kỹ sư (open với các bạn mới tốt nghiệp) cho vị trí về thiết kế và triển khai mạng truyền dẫn tại. Bitel - thương hiệu của Viettel tại Peru, kinh doanh tại thị trường này từ năm 2014.
+VỀ CÔNG VIỆC
+...</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang?locale=vi_VN</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H5" s="1" t="str">
+        <v>2026-09-14 13:33:22</v>
+      </c>
+    </row>
+    <row r="6" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <v>Ho Thuy Trang</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang/posts/2716756185412069/</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <v>thực tập, intern</v>
+      </c>
+      <c r="E6" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">𝗦𝗢𝗔𝗥𝗜𝗚 𝗩𝗜𝗘̣̂𝗧 𝗡𝗔𝗠 𝘁𝘂𝘆𝗲̂̉𝗻 𝗱𝘂̣𝗻𝗴:
+Intern Flutter
+𝐐𝐮𝐲𝐞̂̀𝐧 𝐥𝐨̛̣𝐢:
+- Trợ cấp trong thời gian thực tập
+- Mentor trực tiếp hướng dẫn và hỗ trợ trong quá trình làm việc
+- Được đào tạo, tham gia dự án thực tế của công ty
+- Môi trường làm việc năng động, hỗ trợ học tập và phát t...</v>
+      </c>
+      <c r="F6" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang?locale=vi_VN</v>
+      </c>
+      <c r="G6" s="1" t="str">
+        <v>3 tuần</v>
+      </c>
+      <c r="H6" s="1" t="str">
+        <v>2026-09-14 13:34:15</v>
+      </c>
+    </row>
+    <row r="7" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <v>Truc Ly</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang/posts/2709027309518290/</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <v>chưa có kinh nghiệm</v>
+      </c>
+      <c r="E7" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">FPT TELECOM TUYỂN DỤNG
+NHÂN VIÊN KỸ THUẬT TRIỂN KHAI VÀ BẢO TRÌ DỊCH VỤ VIỄN THÔNG
+ Khu vực làm việc:
+Đà Nẵng
+Quảng Nam: Núi Thành, Tam Kỳ, Thăng Bình, Hà Lam
+ Thu nhập: 10 - 15 triệu/tháng
+ MÔ TẢ CÔNG VIỆC
+• Triển khai, bảo trì và xử lý sự cố dịch vụ Internet, Truyền hình FPT và các dịch vụ viễn th...</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang?locale=vi_VN</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <v>4 tuần</v>
+      </c>
+      <c r="H7" s="1" t="str">
+        <v>2026-09-14 13:34:29</v>
+      </c>
+    </row>
+    <row r="8" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <v>Kim HR</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang/posts/2650040598750295/</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <v>fresher, đào tạo từ đầu</v>
+      </c>
+      <c r="E8" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">CƠ HỘI CHO FRESHER SAP – ONBOARD 07/2026 
+Đào tạo từ đầu – Dự án quốc tế – Làm việc tại Đà Nẵng
+ Làm việc tại: FPT Complex, Nam Kỳ Khởi Nghĩa
+ Thời gian: Full-time
+ Dự kiến bắt đầu: 07/2026
+Bạn mới tốt nghiệp hoặc đang muốn thử sức với SAP? Đây là cơ hội để tiếp cận một trong những hệ thống quản ...</v>
+      </c>
+      <c r="F8" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang?locale=vi_VN</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H8" s="1" t="str">
+        <v>2026-09-14 13:34:47</v>
+      </c>
+    </row>
+    <row r="9" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <v>Truc Ly</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang/posts/2713279315759756/</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <v>chưa có kinh nghiệm</v>
+      </c>
+      <c r="E9" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">FPT TELECOM TUYỂN DỤNG
+NHÂN VIÊN KỸ THUẬT TRIỂN KHAI VÀ BẢO TRÌ DỊCH VỤ VIỄN THÔNG
+ Khu vực làm việc:
+Đà Nẵng
+Quảng Nam: Thăng Bình, Hà Lam
+ Thu nhập: 10 - 25 triệu/tháng
+ MÔ TẢ CÔNG VIỆC
+• Triển khai, bảo trì và xử lý sự cố dịch vụ Internet, Truyền hình FPT và các dịch vụ viễn thông tại nhà khách h...</v>
+      </c>
+      <c r="F9" s="1" t="str">
+        <v>https://www.facebook.com/groups/jobITDaNang?locale=vi_VN</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H9" s="1" t="str">
+        <v>2026-09-14 13:35:29</v>
+      </c>
+    </row>
+    <row r="10" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <v>Ánh Phương Nguyễn</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38199855682993119/</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <v>thực tập, internship</v>
+      </c>
+      <c r="E10" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">INTERNSHIP 2026 – SOLUTION CONSULTANT
+ Bạn sẽ nhận được:
+Thực tập 3 tháng trong môi trường Product, tham gia phân tích bài toán vận hành, thiết kế và xây dựng giải pháp cho doanh nghiệp.
+Được đào tạo về Digital Operations, SaaS, Solution Development và No-code.
+Trợ cấp 1.000.000đ/tháng.
+Cơ hội trở t...</v>
+      </c>
+      <c r="F10" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H10" s="1" t="str">
+        <v>2026-09-14 13:36:09</v>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1" xml:space="preserve">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <v>Trần Chi</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38121917720786916/</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <v>internship, fresher</v>
+      </c>
+      <c r="E11" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">Rikkeisoft đang open khóa Internship/Fresher
+Các vị trí Developer, ưu tiên ứng viên có ngoại ngữ (EN/JP)
+Apply tại Link: https://forms.gle/ssSadnpcGUX7Ra6T8
+#Rikkeisoft #Internship #Japan #Global</v>
+      </c>
+      <c r="F11" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G11" s="1" t="str">
+        <v>3 ngày</v>
+      </c>
+      <c r="H11" s="1" t="str">
+        <v>2026-09-14 13:36:36</v>
+      </c>
+    </row>
+    <row r="12" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <v>Huynh Truc Phuong</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38152702127708475/</v>
+      </c>
+      <c r="D12" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E12" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">HUMAN BRAIN GLOBAL - ĐÀ NẴNG
+Đà Nẵng mưa gió thế này thay vì ra đường thì mọi người ở nhà tham khảo job và update CV, apply các job dưới đây của nhà HBG nha ạ:
+ Scrum Master (Middle), 2+ yoe
+ BrSE (Fresher), JLPT N2+
+ IT Comtor (Middle), 2+ yoe, JLPT N2+
+ Phúc lợi hấp dẫn + môi trường với nhiều dự á...</v>
+      </c>
+      <c r="F12" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H12" s="1" t="str">
+        <v>2026-09-14 13:36:57</v>
+      </c>
+    </row>
+    <row r="13" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="str">
+        <v>Thu Thu</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38148837151428306/</v>
+      </c>
+      <c r="D13" s="1" t="str">
+        <v>chưa có kinh nghiệm</v>
+      </c>
+      <c r="E13" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">𝐙𝐄𝐍𝐃𝐘 𝐑𝐄𝐀𝐋 𝐓𝐔𝐘𝐄̂̉𝐍 𝐃𝐔̣𝐍𝐆 𝐍𝐕 𝐊𝐈𝐍𝐇 𝐃𝐎𝐀𝐍𝐇 𝐍𝐇𝐀̀ Đ𝐀̂́𝐓 𝐓𝐇𝐎̂̉ 𝐂𝐔̛
+𝒀𝒆̂𝒖 𝒄𝒂̂̀𝒖 𝒄𝒐̂𝒏𝒈 𝒗𝒊𝒆̣̂𝒄
+- Nam, Nữ tuổi từ 22-35, sức khỏe tốt
+- Tốt nghiệp từ Cao đẳng
+- Giao tiếp tốt, có laptop và phương tiện đi lại
+- Có kinh nghiệm là một lợi thế
+𝑴𝒐̂ 𝒕𝒂̉ 𝒄𝒐̂𝒏...</v>
+      </c>
+      <c r="F13" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H13" s="1" t="str">
+        <v>2026-09-14 13:37:08</v>
+      </c>
+    </row>
+    <row r="14" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <v>Nguyen Anh Dũng</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38147205421591479/</v>
+      </c>
+      <c r="D14" s="1" t="str">
+        <v>Thực tập sinh, thực tập, không yêu cầu kinh nghiệm</v>
+      </c>
+      <c r="E14" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[ĐÀ NẴNG] Tuyển dụng việc làm Thực Tập Sinh (KHÔNG YÊU CẦU KINH NGHIỆM)
+ MÔ TẢ CÔNG VIỆC
+Hỗ trợ đăng tải nội dung trên các nền tảng mạng xã hội và website.
+Hỗ trợ chụp hình, quay video sản phẩm cơ bản.
+Đón tiếp và tư vấn khách hàng.
+Hỗ trợ tiếp nhận, kiểm tra, phân loại và xử lý hàng hoá.
+Giữ gìn vệ...</v>
+      </c>
+      <c r="F14" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G14" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H14" s="1" t="str">
+        <v>2026-09-14 13:37:13</v>
+      </c>
+    </row>
+    <row r="15" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="str">
+        <v>Trương Tuyền</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38099950586316963/</v>
+      </c>
+      <c r="D15" s="1" t="str">
+        <v>intern</v>
+      </c>
+      <c r="E15" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">WE’RE HIRING | EMPLOYER BRANDING INTERN
+Bạn thích content, truyền thông, sự kiện và hàng tá ý tưởng muốn biến thành hiện thực?
+Bạn muốn một công việc không chỉ “đi làm để học việc”, mà thật sự được hands-on, thử sức và tạo ra những sản phẩm có thể đưa vào portfolio?
+ Đây có thể là cơ hội dành cho b...</v>
+      </c>
+      <c r="F15" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <v>3 ngày</v>
+      </c>
+      <c r="H15" s="1" t="str">
+        <v>2026-09-14 13:37:27</v>
+      </c>
+    </row>
+    <row r="16" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="str">
+        <v>Hoài Linh</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38126090767036278/</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <v>thực tập, intern, internship</v>
+      </c>
+      <c r="E16" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[BAP HUẾ] INTERN INTERNSHIP 2026
+MỘT JOB INTERN - CƠ HỘI THÀNH BAPers SAU 2-3 THÁNG TRAINING NÈ
+Chỉ cần các bạn là
+Sinh viên năm 3,4 / đã tốt nghiệp các ngành thuộc khối công nghệ thông tin/ kinh tế/ ngoại ngữ hoặc liên quan
+Cẩn thận, tỉ mỉ trong công việc
+Năng động, ham học hỏi
+Khả năng thích nghi ...</v>
+      </c>
+      <c r="F16" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G16" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H16" s="1" t="str">
+        <v>2026-09-14 13:37:50</v>
+      </c>
+    </row>
+    <row r="17" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <v>Ho Tran</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38100199739625381/</v>
+      </c>
+      <c r="D17" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E17" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">RIKKEISOFT ĐÀ NẴNG ĐANG TÌM ĐỒNG ĐỘI! 
+Bạn đang tìm kiếm một môi trường để bứt phá chuyên môn, làm dự án công nghệ thực tế và phát triển cùng những đồng đội giỏi?
+Rikkeisoft Đà Nẵng đang mở nhiều vị trí dành cho cả Senior/Middle và các bạn trẻ có nền tảng tốt. 
+ CÁC VỊ TRÍ ĐANG TUYỂN
+ BrSE/PM – JP N...</v>
+      </c>
+      <c r="F17" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <v>3 ngày</v>
+      </c>
+      <c r="H17" s="1" t="str">
+        <v>2026-09-14 13:38:05</v>
+      </c>
+    </row>
+    <row r="18" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <v>Phạm Trâm</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38071368909175131/</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <v>intern, fresher</v>
+      </c>
+      <c r="E18" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[TUYỂN DỤNG MỞ RỘNG TEAM VỚI CÁC VỊ TRÍ TỪ INTERN ĐẾN SENIOR TẠI ĐÀ NẴNG]
+|
+ UI/UX Designer | Intern / Fresher / Junior
+ Android DeveloperFresher / Junior
+ Product Owner (PO)Fresher / Junior
+ User Acquisition (UA)Junior / Senior
+ Monetization (Monet)Junior / Senior
+ 72 Lê Đại Hành, phường Cẩm Lệ, Đà...</v>
+      </c>
+      <c r="F18" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G18" s="1" t="str">
+        <v>4 ngày</v>
+      </c>
+      <c r="H18" s="1" t="str">
+        <v>2026-09-14 13:38:47</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <v>Nhok Kieumy</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38103458439299511/</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <v>[DN- HN] em cần gấp fresher IT comtor hoặc các bạn có tiếng Nhật tốt. Được làm dự án + tranning + benefits hấp dẫn. Ib ngay ạ</v>
+      </c>
+      <c r="F19" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H19" s="1" t="str">
+        <v>2026-09-14 13:39:05</v>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1" xml:space="preserve">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <v>Quang Nguyễn</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew/posts/38101314906180531/</v>
+      </c>
+      <c r="D20" s="1" t="str">
+        <v>fresher, đào tạo từ đầu</v>
+      </c>
+      <c r="E20" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUYỂN NHÂN VIÊN TRIỂN KHAI WEBSITE (FRESHER)
+Solvia đang tìm bạn trẻ yêu thích việc dựng website nhanh, đẹp, đúng yêu cầu khách hàng bằng công cụ page builder trên nền tảng Joomla. Đây không phải vị trí lập trình viên (developer) — công việc chính là cấu hình, kéo-thả, tùy biến giao diện và nội dung...</v>
+      </c>
+      <c r="F20" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdanangnew?locale=vi_VN</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H20" s="1" t="str">
+        <v>2026-09-14 13:39:10</v>
+      </c>
+    </row>
+    <row r="21" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <v>Ánh Phương Nguyễn</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2877602105946898/</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <v>thực tập, internship</v>
+      </c>
+      <c r="E21" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">INTERNSHIP 2026 – SOLUTION CONSULTANT
+Bạn muốn bắt đầu sự nghiệp trong Công nghệ, SaaS &amp; Chuyển đổi số?
+ Bạn sẽ nhận được:
+Thực tập 3 tháng, được đào tạo về SaaS, Digital Operations &amp; No-code.
+Trực tiếp tham gia phân tích và xây dựng giải pháp cho doanh nghiệp.
+Trợ cấp 1.000.000đ/tháng.
+Cơ hội trở ...</v>
+      </c>
+      <c r="F21" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H21" s="1" t="str">
+        <v>2026-09-14 13:39:34</v>
+      </c>
+    </row>
+    <row r="22" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="str">
+        <v>Quyền Thái Trương</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2849958765377899/</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <v>không yêu cầu kinh nghiệm</v>
+      </c>
+      <c r="E22" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">#Tuyểndụng
+#Nhânviênkỹthuật
+#Thựctậpsinh
+#Họcviệc
+1. Số lượng: 4
+2. Mô tả công việc:
+- Triển khai thi công hệ thống Điện - Nước - Điện nhẹ công trình.
+3. Yêu cầu:
+- Không yêu cầu kinh nghiệm.
+- Ưu tiên ứng viên đã qua đào tạo về Điện - Điện tử - CNTT - Cấp thoát nước - Kỹ thuật ...
+- Đã hoàn thành N...</v>
+      </c>
+      <c r="F22" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <v>3 tuần</v>
+      </c>
+      <c r="H22" s="1" t="str">
+        <v>2026-09-14 13:39:43</v>
+      </c>
+    </row>
+    <row r="23" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="str">
+        <v>Huong Ha</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2877154462658329/</v>
+      </c>
+      <c r="D23" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E23" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[Đà Nẵng] Công ty công nghệ SmartOSC - Tuyển dụng 02 vị trí Fresher
+- Fresher Nodejs Developer
+- Fresher AI Engineer
+ Quyền lợi:
+- Thời gian làm việc linh hoạt từ T2-T6.
+- Được trợ cấp upto 6 triệu/tháng.
+- Có cơ hội lên nhân viên chính thức sau 3 tháng, thu nhập 1x triệu gross
+- Tham gia các dự án ...</v>
+      </c>
+      <c r="F23" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G23" s="1" t="str">
+        <v>15 giờ</v>
+      </c>
+      <c r="H23" s="1" t="str">
+        <v>2026-09-14 13:39:55</v>
+      </c>
+    </row>
+    <row r="24" ht="90" customHeight="1" xml:space="preserve">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="str">
+        <v>Quang Nguyễn</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2877625875944521/</v>
+      </c>
+      <c r="D24" s="1" t="str">
+        <v>fresher, đào tạo từ đầu</v>
+      </c>
+      <c r="E24" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUYỂN NHÂN VIÊN TRIỂN KHAI WEBSITE (FRESHER)
+Solvia đang tìm bạn trẻ yêu thích việc dựng website nhanh, đẹp, đúng yêu cầu khách hàng bằng công cụ page builder trên nền tảng Joomla. Đây không phải vị trí lập trình viên (developer) — công việc chính là cấu hình, kéo-thả, tùy biến giao diện và nội dung...</v>
+      </c>
+      <c r="F24" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H24" s="1" t="str">
+        <v>2026-09-14 13:40:22</v>
+      </c>
+    </row>
+    <row r="25" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="str">
+        <v>Truc Ly</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2877586715948437/</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <v>chưa có kinh nghiệm</v>
+      </c>
+      <c r="E25" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">FPT TELECOM TUYỂN DỤNG
+1. KỸ THUẬT ĐIỀU HÀNH
+2. NHÂN VIÊN KỸ THUẬT TRIỂN KHAI VÀ BẢO TRÌ DỊCH VỤ VIỄN THÔNG
+ Khu vực làm việc:
+Đà Nẵng
+Quảng Nam
+ Thu nhập: 15 - 20 triệu/tháng
+ MÔ TẢ CÔNG VIỆC
+1.KỸ THUẬT ĐIỀU HÀNH
+Điều phối, giám sát đội ngũ kỹ thuật triển khai và bảo trì dịch vụ viễn thông.
+Lập kế ...</v>
+      </c>
+      <c r="F25" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G25" s="1" t="str">
+        <v>4 giờ</v>
+      </c>
+      <c r="H25" s="1" t="str">
+        <v>2026-09-14 13:40:25</v>
+      </c>
+    </row>
+    <row r="26" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="str">
+        <v>PlayfulHeron9225</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2876954032678372/</v>
+      </c>
+      <c r="D26" s="1" t="str">
+        <v>không yêu cầu kinh nghiệm</v>
+      </c>
+      <c r="E26" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUYỂN NHÂN VIÊN SẢN XUẤT NỘI DUNG GAME
+Team đang tìm kiếm 02 bạn nữ tham gia sản xuất nội dung game 
+ CÔNG VIỆC
+• Chơi game và quay lại quá trình chơi trên máy tính
+• Xây dựng các câu chuyện trong game theo chủ đề được giao.
+• Thực hiện nội dung theo hướng dẫn của team.
+• Được training và hướng dẫn ...</v>
+      </c>
+      <c r="F26" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <v>18 giờ</v>
+      </c>
+      <c r="H26" s="1" t="str">
+        <v>2026-09-14 13:40:38</v>
+      </c>
+    </row>
+    <row r="27" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="str">
+        <v>Viet Nguyen</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2870747229965719/</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <v>Thực tập sinh, thực tập, intern, fresher</v>
+      </c>
+      <c r="E27" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[ITDRAGONS] TUYỂN DỤNG FULL-STACK JAVA DEVELOPER (INTERN / FRESHER / JUNIOR)
+ Địa điểm: 127 Phạm Văn Xảo, P. Sơn Trà, Đà Nẵng
+ Hình thức: Toàn thời gian (Full-time) / Thực tập sinh
+ Thu nhập:
+Intern: Hỗ trợ đào tạo (tối đa 3 tháng)
+Fresher: 3-5 triệu (tối đa 3 tháng)
+Junior: 7-11 triệu (2 tháng thử ...</v>
+      </c>
+      <c r="F27" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <v>6 ngày</v>
+      </c>
+      <c r="H27" s="1" t="str">
+        <v>2026-09-14 13:40:40</v>
+      </c>
+    </row>
+    <row r="28" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="str">
+        <v>Hoài Linh</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2874860459554396/</v>
+      </c>
+      <c r="D28" s="1" t="str">
+        <v>thực tập, intern, internship</v>
+      </c>
+      <c r="E28" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[BAP HUẾ] INTERN INTERNSHIP 2026
+MỘT JOB INTERN - CƠ HỘI THÀNH BAPers SAU 2-3 THÁNG TRAINING NÈ
+Chỉ cần các bạn là
+Sinh viên năm 3,4 / đã tốt nghiệp các ngành thuộc khối công nghệ thông tin/ kinh tế/ ngoại ngữ hoặc liên quan
+Cẩn thận, tỉ mỉ trong công việc
+Năng động, ham học hỏi
+Khả năng thích nghi ...</v>
+      </c>
+      <c r="F28" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G28" s="1" t="str">
+        <v>1 ngày</v>
+      </c>
+      <c r="H28" s="1" t="str">
+        <v>2026-09-14 13:41:09</v>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="str">
+        <v>CourteousGrape5233</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2875978406109268/</v>
+      </c>
+      <c r="D29" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <v>Có bác nào apply fresher dev bên vnpt it đà nẵng không ạ, cho mình hỏi các bác có mail pv chưa. Mình nộp 2 tuần r chưa có thông tin gì k biết fail không. Cảm ơn mn.</v>
+      </c>
+      <c r="F29" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <v>1 ngày</v>
+      </c>
+      <c r="H29" s="1" t="str">
+        <v>2026-09-14 13:41:14</v>
+      </c>
+    </row>
+    <row r="30" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="str">
+        <v>Ngân Khánh</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2871504489889993/</v>
+      </c>
+      <c r="D30" s="1" t="str">
+        <v>chưa có kinh nghiệm</v>
+      </c>
+      <c r="E30" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">TUYỂN DỤNG UNITY DEVELOPER – GAME KIẾM THẾ MOBILE 2009
+ Hình thức làm việc: Remote
+ Dự án: Kiếm Thế Mobile – phiên bản Classic 2009
+Chúng tôi đang tìm kiếm Unity Developer có kinh nghiệm thực tế với dòng game Kiếm Thế Mobile để đồng hành và phát triển dự án lâu dài.
+ MÔ TẢ CÔNG VIỆC
+* Cấu hình, vận ...</v>
+      </c>
+      <c r="F30" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G30" s="1" t="str">
+        <v>5 ngày</v>
+      </c>
+      <c r="H30" s="1" t="str">
+        <v>2026-09-14 13:41:26</v>
+      </c>
+    </row>
+    <row r="31" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="str">
+        <v>阮氏 碧行</v>
+      </c>
+      <c r="C31" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2875880666119042/</v>
+      </c>
+      <c r="D31" s="1" t="str">
+        <v>Thực tập sinh, thực tập, tuyển thực tập, chưa có kinh nghiệm</v>
+      </c>
+      <c r="E31" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[ĐÀ NẴNG] THE LEAD AGENCY TUYỂN THỰC TẬP SINH SOCIAL CONTENT
+The Lead Agency đang tìm kiếm Thực tập sinh Social Content dành cho các bạn sinh viên năm 4/năm cuối muốn tích lũy kinh nghiệm thực tế trong lĩnh vực Content &amp; Digital Marketing.
+VỊ TRÍ: THỰC TẬP SINH SOCIAL CONTENT
+Bộ phận: Marketing
+Hình...</v>
+      </c>
+      <c r="F31" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G31" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H31" s="1" t="str">
+        <v>2026-09-14 13:41:45</v>
+      </c>
+    </row>
+    <row r="32" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="str">
+        <v>Huynh Truc Phuong</v>
+      </c>
+      <c r="C32" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2875869312786844/</v>
+      </c>
+      <c r="D32" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E32" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">HUMAN BRAIN GLOBAL - ĐÀ NẴNG
+Đà Nẵng mưa gió thế này thay vì ra đường thì mọi người ở nhà tham khảo job và update CV, apply các job dưới đây của nhà HBG nha ạ:
+ Scrum Master (Middle), 2+ yoe
+ BrSE (Fresher), JLPT N2+
+ IT Comtor (Middle), 2+ yoe, JLPT N2+
+ Phúc lợi hấp dẫn + môi trường với nhiều dự á...</v>
+      </c>
+      <c r="F32" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G32" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H32" s="1" t="str">
+        <v>2026-09-14 13:41:49</v>
+      </c>
+    </row>
+    <row r="33" ht="144" customHeight="1" xml:space="preserve">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="str">
+        <v>Nguyen Anh Dũng</v>
+      </c>
+      <c r="C33" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2875660592807716/</v>
+      </c>
+      <c r="D33" s="1" t="str">
+        <v>Thực tập sinh, thực tập, không yêu cầu kinh nghiệm</v>
+      </c>
+      <c r="E33" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[ĐÀ NẴNG] Tuyển dụng việc làm Thực Tập Sinh (KHÔNG YÊU CẦU KINH NGHIỆM)
+ MÔ TẢ CÔNG VIỆC
+Hỗ trợ đăng tải nội dung trên các nền tảng mạng xã hội và website.
+Hỗ trợ chụp hình, quay video sản phẩm cơ bản.
+Đón tiếp và tư vấn khách hàng.
+Hỗ trợ tiếp nhận, kiểm tra, phân loại và xử lý hàng hoá.
+Giữ gìn vệ...</v>
+      </c>
+      <c r="F33" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G33" s="1" t="str">
+        <v>2 ngày</v>
+      </c>
+      <c r="H33" s="1" t="str">
+        <v>2026-09-14 13:41:58</v>
+      </c>
+    </row>
+    <row r="34" ht="90" customHeight="1" xml:space="preserve">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="str">
+        <v>Trần Chi</v>
+      </c>
+      <c r="C34" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2874683632905412/</v>
+      </c>
+      <c r="D34" s="1" t="str">
+        <v>internship, fresher</v>
+      </c>
+      <c r="E34" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">RIKKEI ĐÀ NẴNG ĐANG TUYỂN INTERNSHIP/FRESHER
+Thời gian nhận CV: 11/9 - 18/9/2026
+Rikkeisoft Đà Nẵng - 81 Quang Trung, Hải Châu, Đà Nẵng
+Ứng Tuyển: https://forms.gle/AoeH31MZ2ogp79DU8
+JD được đính kèm tại link ứng tuyển</v>
+      </c>
+      <c r="F34" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G34" s="1" t="str">
+        <v>3 ngày</v>
+      </c>
+      <c r="H34" s="1" t="str">
+        <v>2026-09-14 13:42:09</v>
+      </c>
+    </row>
+    <row r="35" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="str">
+        <v>Thanh Trâm HR</v>
+      </c>
+      <c r="C35" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2866594033714372/</v>
+      </c>
+      <c r="D35" s="1" t="str">
+        <v>không yêu cầu kinh nghiệm</v>
+      </c>
+      <c r="E35" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">FPT SOFTWARE ĐÀ NẴNG TUYỂN 10 CTV XỬ LÝ ẢNH
+ Làm việc tại FPT Massda – Sơn Trà, Đà Nẵng| OB đầu tháng 10
+ Không yêu cầu kinh nghiệm – nếu bạn thao tác máy tính tốt và muốn tìm một công việc ổn định, apply ngay nhé!
+ Công việc:
+• Gắn nhãn, đóng khung, tô màu, chấm điểm đối tượng trên hình ảnh
+• X...</v>
+      </c>
+      <c r="F35" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <v>1 tuần</v>
+      </c>
+      <c r="H35" s="1" t="str">
+        <v>2026-09-14 13:42:12</v>
+      </c>
+    </row>
+    <row r="36" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="str">
+        <v>Hậu Lê</v>
+      </c>
+      <c r="C36" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2873810476326061/</v>
+      </c>
+      <c r="D36" s="1" t="str">
+        <v>fresher</v>
+      </c>
+      <c r="E36" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[AVEPOINT] CHIÊU MỘ FRESHER- JUNIOR IT, THỬ VIỆC, BHXH FULL LƯƠNG
+Bạn đang tìm kiếm một môi trường global, chuyên nghiệp, có nhiều cơ hội phát triển và phúc lợi tốt, tham khảo ngay các vị trí đến từ AvePoint Hà Nội/ Đà Nẵng và Hồ Chí Minh ngay thôi!
+ CÁC VỊ TRÍ ĐANG TUYỂN
+ IT Engineer (IT Infrast...</v>
+      </c>
+      <c r="F36" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G36" s="1" t="str">
+        <v>2 ngày</v>
+      </c>
+      <c r="H36" s="1" t="str">
+        <v>2026-09-14 13:42:18</v>
+      </c>
+    </row>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="str">
+        <v>NiftyCrocodile8241</v>
+      </c>
+      <c r="C37" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn/posts/2826506331056476/</v>
+      </c>
+      <c r="D37" s="1" t="str">
+        <v>thực tập, fresher</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <v>Chào mọi người, em là sinh viên ĐTVT đại học Bách Khoa Đà Nẵng. Hiện em đang chờ bằng và có mong muốn được apply vào vị trí fresher hardware design. Em đã có kinh nghiệm thức tập 6 tháng ở dự án R&amp;D với vị trí embedded software, được tham gia thiết kế schematic, layout pcb cũng như phát triển firmwa...</v>
+      </c>
+      <c r="F37" s="1" t="str">
+        <v>https://www.facebook.com/groups/vieclamcnttdn?locale=vi_VN</v>
+      </c>
+      <c r="G37" s="1" t="str">
+        <v>2 ngày</v>
+      </c>
+      <c r="H37" s="1" t="str">
+        <v>2026-09-14 13:42:45</v>
+      </c>
+    </row>
+    <row r="38" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="str">
+        <v>Nhà đất Liên Chiểu- Đà Nẵng</v>
+      </c>
+      <c r="C38" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124/posts/2070619126924607/</v>
+      </c>
+      <c r="D38" s="1" t="str">
+        <v>chưa có kinh nghiệm</v>
+      </c>
+      <c r="E38" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">TEAM LY MỞ RỘNG ĐỘI NGŨ – BẤT ĐỘNG SẢN MIỀN TRUNG 
+ Cơ hội dành cho ACE muốn bước vào nghề BĐS, nâng cao thu nhập và phát triển lâu dài!
+ TEAM LY ĐANG TUYỂN:
+ Chuyên viên Sale BĐS
+ Cộng tác viên
+ Trợ lý tuyển dụng
+ Trưởng phòng
+ Đầu chủ
+ VỀ TEAM LY, ACE ĐƯỢC:
+ Đào tạo &amp; cầm tay chỉ việc thực tế
+ Hỗ ...</v>
+      </c>
+      <c r="F38" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124?locale=vi_VN</v>
+      </c>
+      <c r="G38" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H38" s="1" t="str">
+        <v>2026-09-14 13:44:08</v>
+      </c>
+    </row>
+    <row r="39" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="str">
+        <v>Hương Thanh</v>
+      </c>
+      <c r="C39" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124/posts/2070510786935441/</v>
+      </c>
+      <c r="D39" s="1" t="str">
+        <v>intern</v>
+      </c>
+      <c r="E39" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">ZAUBERBERG LAB | OPEN POSITION: INFLUENCER MARKETING INTERN 
+Bạn muốn thử sức với Marketing quốc tế và làm việc trực tiếp với các Creator trên toàn cầu?
+ Về Zauberberg Lab
+Zauberberg Lab là đội ngũ đứng sau CollaNote – ứng dụng ghi chú hàng đầu trên iPad cùng nhiều sản phẩm giáo dục sáng tạo khác.
+C...</v>
+      </c>
+      <c r="F39" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124?locale=vi_VN</v>
+      </c>
+      <c r="G39" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H39" s="1" t="str">
+        <v>2026-09-14 13:44:17</v>
+      </c>
+    </row>
+    <row r="40" ht="126" customHeight="1" xml:space="preserve">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="str">
+        <v>Hương Thanh</v>
+      </c>
+      <c r="C40" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124/posts/2070510500268803/</v>
+      </c>
+      <c r="D40" s="1" t="str">
+        <v>intern</v>
+      </c>
+      <c r="E40" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">ZAUBERBERG LAB | OPEN POSITION: INFLUENCER MARKETING INTERN 
+Bạn muốn thử sức với Marketing quốc tế và làm việc trực tiếp với các Creator trên toàn cầu?
+ Về Zauberberg Lab
+Zauberberg Lab là đội ngũ đứng sau CollaNote – ứng dụng ghi chú hàng đầu trên iPad cùng nhiều sản phẩm giáo dục sáng tạo khác.
+C...</v>
+      </c>
+      <c r="F40" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124?locale=vi_VN</v>
+      </c>
+      <c r="G40" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H40" s="1" t="str">
+        <v>2026-09-14 13:44:21</v>
+      </c>
+    </row>
+    <row r="41" ht="160" customHeight="1" xml:space="preserve">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="str">
+        <v>Phạm Trâm</v>
+      </c>
+      <c r="C41" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124/posts/2069579063695280/</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <v>intern, fresher</v>
+      </c>
+      <c r="E41" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">[TUYỂN DỤNG MỞ RỘNG TEAM VỚI CÁC VỊ TRÍ TỪ INTERN ĐẾN SENIOR TẠI ĐÀ NẴNG]
+|
+ UI/UX Designer | Intern / Fresher / Junior
+ Android DeveloperFresher / Junior
+ Product Owner (PO)Fresher / Junior
+ User Acquisition (UA)Junior / Senior
+ Monetization (Monet)Junior / Senior
+ : 72 Lê Đại Hành, phường Cẩm Lệ, ...</v>
+      </c>
+      <c r="F41" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124?locale=vi_VN</v>
+      </c>
+      <c r="G41" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H41" s="1" t="str">
+        <v>2026-09-14 13:45:37</v>
+      </c>
+    </row>
+    <row r="42" ht="108" customHeight="1" xml:space="preserve">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="str">
+        <v>Hương Thanh</v>
+      </c>
+      <c r="C42" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124/posts/2068790500440803/</v>
+      </c>
+      <c r="D42" s="1" t="str">
+        <v>intern</v>
+      </c>
+      <c r="E42" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">ZAUBERBERG LAB | TUYỂN DỤNG MARKETING INTERN 
+Global Product | Làm việc tại Đà Nẵng 
+ Về Zauberberg Lab
+Zauberberg Lab là đội ngũ phát triển CollaNote - ứng dụng ghi chú trên iPad được Apple vinh danh tại hạng mục “Big App from Small Team”.
+Hiện ZLab đang mở rộng team Marketing tại Đà Nẵng, tìm kiếm...</v>
+      </c>
+      <c r="F42" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124?locale=vi_VN</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <v/>
+      </c>
+      <c r="H42" s="1" t="str">
+        <v>2026-09-14 13:46:15</v>
+      </c>
+    </row>
+    <row r="43" ht="108" customHeight="1" xml:space="preserve">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="str">
+        <v>Huỳnh Thị Hiếu</v>
+      </c>
+      <c r="C43" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124/posts/2068040550515798/</v>
+      </c>
+      <c r="D43" s="1" t="str">
+        <v>chưa có kinh nghiệm, không yêu cầu kinh nghiệm, đào tạo từ đầu</v>
+      </c>
+      <c r="E43" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">HỌC CNTT 4 NĂM, RA TRƯỜNG… VẪN CHƯA TÌM ĐƯỢC JOB ĐÚNG NGÀNH?
+ Ở Đà Nẵng, nếu đang loay hoay tìm việc và bắt đầu nghĩ đến một công việc trái ngành, thì đừng vội nghĩ đó là bước lùi.
+ Bạn có thể không trở thành lập trình viên, nhưng những kỹ năng bạn có từ CNTT vẫn là lợi thế khi bước sang lĩnh vực K...</v>
+      </c>
+      <c r="F43" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124?locale=vi_VN</v>
+      </c>
+      <c r="G43" s="1" t="str">
+        <v>6 ngày</v>
+      </c>
+      <c r="H43" s="1" t="str">
+        <v>2026-09-14 13:46:47</v>
+      </c>
+    </row>
+    <row r="44" ht="108" customHeight="1" xml:space="preserve">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="str">
+        <v>Huỳnh Thị Hiếu</v>
+      </c>
+      <c r="C44" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124/posts/2068033370516516/</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <v>chưa có kinh nghiệm, không yêu cầu kinh nghiệm, đào tạo từ đầu</v>
+      </c>
+      <c r="E44" s="1" t="str" xml:space="preserve">
+        <v xml:space="preserve">HỌC CNTT 4 NĂM, RA TRƯỜNG… VẪN CHƯA TÌM ĐƯỢC JOB ĐÚNG NGÀNH?
+ Ở Đà Nẵng, nếu đang loay hoay tìm việc và bắt đầu nghĩ đến một công việc trái ngành, thì đừng vội nghĩ đó là bước lùi.
+ Bạn có thể không trở thành lập trình viên, nhưng những kỹ năng bạn có từ CNTT vẫn là lợi thế khi bước sang lĩnh vực K...</v>
+      </c>
+      <c r="F44" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124?locale=vi_VN</v>
+      </c>
+      <c r="G44" s="1" t="str">
+        <v>6 ngày</v>
+      </c>
+      <c r="H44" s="1" t="str">
+        <v>2026-09-14 13:46:50</v>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="str">
+        <v>Test Hyperlink Author</v>
+      </c>
+      <c r="C45" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124/posts/2068603323792854/</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <v>intern</v>
+      </c>
+      <c r="E45" s="1" t="str">
+        <v>Kiểm tra tính năng tự động tạo Hyperlink có thể bấm click trực tiếp.</v>
+      </c>
+      <c r="F45" s="1" t="str">
+        <v>https://www.facebook.com/groups/1261520704501124</v>
+      </c>
+      <c r="G45" s="1" t="str">
+        <v>Thứ Hai, 14 Tháng 9, 2026</v>
+      </c>
+      <c r="H45" s="1" t="str">
+        <v>2026-09-14 14:41:00</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H45"/>
+  </ignoredErrors>
 </worksheet>
 </file>